--- a/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor</t>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,54</t>
+          <t>0,25; 2,62</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,77</t>
+          <t>0,26; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,64</t>
+          <t>0,14; 2,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,09</t>
+          <t>0,44; 2,12</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,55</t>
+          <t>0,9; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,69</t>
+          <t>1,36; 6,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,89</t>
+          <t>1,48; 4,79</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,1</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,92</t>
+          <t>0,31; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,76</t>
+          <t>0,66; 2,99</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,68</t>
+          <t>0,89; 2,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,57</t>
+          <t>0,9; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,26</t>
+          <t>1,03; 2,17</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1572</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5077</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4644</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>634; 6745</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>501; 5038</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>363; 7252</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1957; 9466</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5027</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5615</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10643</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1697; 10519</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2527; 12422</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5553; 17974</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>569; 7646</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2303; 10451</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5914; 16840</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6848; 19006</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14731; 31003</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,62</t>
+          <t>0,23; 2,67</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,64</t>
+          <t>0,27; 2,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,84</t>
+          <t>0,14; 2,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,12</t>
+          <t>0,44; 2,11</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,55</t>
+          <t>0,98; 5,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,7</t>
+          <t>1,32; 6,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,79</t>
+          <t>1,62; 4,82</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,34; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,22</t>
+          <t>0,5; 4,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,99</t>
+          <t>0,58; 3,13</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,53</t>
+          <t>0,9; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,5</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,17</t>
+          <t>1,09; 2,22</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor (tasa de respuesta: 99,95%)</t>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5077</t>
+          <t>0; 5735</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634; 6745</t>
+          <t>593; 6867</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>501; 5038</t>
+          <t>510; 5400</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>363; 7252</t>
+          <t>361; 7496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1957; 9466</t>
+          <t>1967; 9416</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1697; 10519</t>
+          <t>1854; 10082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2527; 12422</t>
+          <t>2442; 11744</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5553; 17974</t>
+          <t>6060; 18066</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5265</t>
+          <t>567; 5396</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>569; 7646</t>
+          <t>899; 7515</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2303; 10451</t>
+          <t>2012; 10937</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5914; 16840</t>
+          <t>5973; 16943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6848; 19006</t>
+          <t>6812; 19822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14731; 31003</t>
+          <t>15480; 31705</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,67</t>
+          <t>0,23; 2,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,83</t>
+          <t>0,2; 2,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,94</t>
+          <t>0,37; 2,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,11</t>
+          <t>0,41; 2,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,32</t>
+          <t>1,43; 7,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,34</t>
+          <t>1,5; 6,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,82</t>
+          <t>1,93; 5,49</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,21</t>
+          <t>0,53; 4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,15</t>
+          <t>0,29; 2,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,13</t>
+          <t>0,52; 2,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,55</t>
+          <t>0,92; 2,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>0,99; 2,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,22</t>
+          <t>1,12; 2,38</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2726</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5735</t>
+          <t>0; 3731</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 5825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>593; 6867</t>
+          <t>570; 6957</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4070</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>510; 5400</t>
+          <t>474; 6783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>361; 7496</t>
+          <t>679; 5088</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1967; 9416</t>
+          <t>1732; 9203</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10513</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1854; 10082</t>
+          <t>2405; 12001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2442; 11744</t>
+          <t>2348; 10705</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6060; 18066</t>
+          <t>6258; 17821</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4628</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>567; 5396</t>
+          <t>902; 6954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>899; 7515</t>
+          <t>489; 4864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2012; 10937</t>
+          <t>1749; 9239</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5973; 16943</t>
+          <t>6463; 19047</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6812; 19822</t>
+          <t>6234; 17946</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15480; 31705</t>
+          <t>14947; 31695</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP13_R1_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,98</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,81</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 2,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 2,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 2,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,41; 2,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 7,13</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 6,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,93; 5,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,53; 4,11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 2,91</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 2,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 2,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,99; 2,85</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 2,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.008640064905373548</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.0135660229624034</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.01106008869601482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2726</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.002311017300059846</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3731</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5825</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>570; 6957</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.02976075164592371</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.04810870824087</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.0282291760261168</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.009181509111563664</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01025780972915265</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.009652274180908402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2178</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1892</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4070</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.001999926416844794</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.003682644001501987</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.004108946904809454</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>474; 6783</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>679; 5088</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1732; 9203</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.02859411235084402</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.02759049190418787</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02182834747505626</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.03172302866072925</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.03311478874288297</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.03239288529175699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10513</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.01428651463390035</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01503003239668365</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01928327482052819</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2405; 12001</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2348; 10705</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6258; 17821</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.07129040263618221</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06853180157631178</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.05491055409472825</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01651297889778891</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01095308593718113</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01375146774554336</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.005325186489026512</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.002924333053206083</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.00519704615980798</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>902; 6954</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>489; 4864</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1749; 9239</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.04105644973802549</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02910252968985211</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02745382207719049</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01627647939490868</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01675730457722871</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01650396627336009</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>11398</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>10538</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21936</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.009228946470148621</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.009913507837601931</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01124559150521213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6463; 19047</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6234; 17946</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14947; 31695</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02719846505330167</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.02853823238181116</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02384663201447618</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1083</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1642</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3731</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5825</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6957</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>2178</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1892</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>474</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>679</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>6783</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>5088</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>9203</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>5340</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5173</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>10513</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>2405</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>6258</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>12001</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>10705</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>17821</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2797</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>902</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>489</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>6954</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>4864</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>9239</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>11398</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>10538</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>21936</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>6234</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>14947</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>19047</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>17946</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>31695</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>